--- a/archivos/archivo_comentario (1).xlsx
+++ b/archivos/archivo_comentario (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8baac22e12d38f5c/Documents/GitHub/simulador-propagacion-emocional/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_61B45DD85F6CC18749FB8F6C24297C5A43DC6F01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CED1AFE3-8A28-4747-B347-278B9D43F792}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_61B45DD85F6CC18749FB8F6C24297C5A43DC6F01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCBFFA51-B667-4331-A2B9-E4FADAAB7F6A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>id_situacion</t>
   </si>
@@ -41,9 +41,6 @@
   </si>
   <si>
     <t>a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">False </t>
   </si>
   <si>
     <t>b</t>
@@ -158,6 +155,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,20 +398,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" ht="87" customHeight="1" x14ac:dyDescent="0.25">
@@ -418,20 +415,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -439,20 +432,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
@@ -460,20 +449,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
@@ -481,20 +466,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="1"/>
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
@@ -502,20 +483,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="1"/>
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
@@ -523,20 +500,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="1"/>
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
@@ -544,18 +517,14 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="1"/>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
@@ -563,20 +532,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>

--- a/archivos/archivo_comentario (1).xlsx
+++ b/archivos/archivo_comentario (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8baac22e12d38f5c/Documents/GitHub/simulador-propagacion-emocional/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_61B45DD85F6CC18749FB8F6C24297C5A43DC6F01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCBFFA51-B667-4331-A2B9-E4FADAAB7F6A}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_61B45DD85F6CC18749FB8F6C24297C5A43DC6F01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4DBEEE-A206-44DE-8B05-F69F9D57558F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>id_situacion</t>
   </si>
@@ -49,9 +49,6 @@
     <t>c</t>
   </si>
   <si>
-    <t>"Está buena la idea según la profesora pero esta toda mal desarrollada, nos dio la clase pero la tenemos que aprovechar y corregir todo hoy porque sino no vamos a poder avanzar nada."</t>
-  </si>
-  <si>
     <t>Entrega de trabajo practico</t>
   </si>
   <si>
@@ -67,19 +64,25 @@
     <t>Agregan una presentacion oral al cronograma</t>
   </si>
   <si>
-    <t>Tenemos muy poco tiempo para prepararla, que nervios hablar en frente de todos!</t>
-  </si>
-  <si>
-    <t>Que bueno que entendemos el trabajo, lo vamos a poder explicar re bien</t>
-  </si>
-  <si>
-    <t>Tranqui, no nos estresemos son nuestros companeros y sabemos el trabajo</t>
-  </si>
-  <si>
     <t>La profesora agrego un tema para el final</t>
   </si>
   <si>
-    <t>Uhh no llegamos a estudiarlo, hay muy poco tiempo</t>
+    <t>No lo puedo creer, ya estaba complicado el final y ahora agregan otro tema más. Siento que no voy a llegar a estudiar todo.</t>
+  </si>
+  <si>
+    <t>Bueno, es un tema más, pero todavía tenemos tiempo para organizarnos. Si nos repartimos los apuntes y estudiamos juntos, podemos llegar bien.</t>
+  </si>
+  <si>
+    <t>No se preocupen tanto. Ya tenemos bastante de la materia vista y es solo un tema adicional. Vamos paso a paso y seguro sale bien.</t>
+  </si>
+  <si>
+    <t>Ya estaba bastante cargado con los trabajos y exámenes, esto me está poniendo muy nervioso.</t>
+  </si>
+  <si>
+    <t>Bueno, una presentación oral también es una oportunidad para demostrar lo que sabemos. Si nos preparamos con tiempo y practicamos juntos, nos va a salir bien.</t>
+  </si>
+  <si>
+    <t>No pasa nada, todavía falta bastante para la presentación. Si organizamos el trabajo desde ahora, vamos a llegar tranquilos y preparados.</t>
   </si>
 </sst>
 </file>
@@ -398,13 +401,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -415,13 +418,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -432,13 +435,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -449,13 +452,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1"/>
@@ -466,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="1"/>
@@ -483,13 +486,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="1"/>
@@ -500,13 +503,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="1"/>
@@ -517,12 +520,14 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="1"/>
       <c r="G9" s="3"/>
@@ -532,13 +537,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="1"/>
